--- a/Daily scrum - aknakereső.xlsx
+++ b/Daily scrum - aknakereső.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://turristvanszakkozepisk-my.sharepoint.com/personal/adolfaron_turr_hu/Documents/Órák/IKT/aknakereso_AA_DB_TZ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adolfaron\source\repos\aknakereso_AA_DB_TZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{B87417E3-801A-460A-B3A9-DBF8521E0A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E0CB3F-7FBF-48DA-AA11-BF34665AF0FB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE757FE-2B6E-4E8F-96EB-359BD6F57979}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1598DC0C-8656-4279-91FD-70E13BBE3EF4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9525" xr2:uid="{1598DC0C-8656-4279-91FD-70E13BBE3EF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -74,9 +63,6 @@
     <t>kattintás kezelése (terjedés)</t>
   </si>
   <si>
-    <t>dokumentációk elkészítése</t>
-  </si>
-  <si>
     <t>menü lehetőségek</t>
   </si>
   <si>
@@ -102,13 +88,16 @@
   </si>
   <si>
     <t>kód átnézése, hibák javítása, dokumentácuók elkezdése</t>
+  </si>
+  <si>
+    <t>dokumentációk elkészítése, tesztelés</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,67 +169,58 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -250,6 +230,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -586,228 +575,228 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E5CB74-2367-49FA-89CF-72C771E9CE7D}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.08984375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="s">
+    <row r="1" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+    <row r="2" spans="1:4">
+      <c r="A2" s="17">
         <v>46162</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="17"/>
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="15"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="18"/>
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="18" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="16">
         <v>46163</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="17"/>
+      <c r="B6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="15"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="18"/>
+      <c r="B7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" s="16">
         <v>46169</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10" t="s">
+      <c r="D8" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="17"/>
+      <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="26"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="18"/>
+      <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="22"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="16">
         <v>46163</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="17"/>
+      <c r="B12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="18"/>
+      <c r="B13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="27"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="17">
+        <v>46170</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="17"/>
+      <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14" t="s">
+      <c r="C15" s="23"/>
+      <c r="D15" s="26"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="18"/>
+      <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="22"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
-        <v>46170</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="C16" s="24"/>
+      <c r="D16" s="27"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="17">
+        <v>46174</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C17" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D17" s="25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10" t="s">
+    <row r="18" spans="1:4">
+      <c r="A18" s="17"/>
+      <c r="B18" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14" t="s">
+      <c r="C18" s="23"/>
+      <c r="D18" s="26"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="18"/>
+      <c r="B19" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="22"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="9">
-        <v>46174</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="22"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="27"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="19">
